--- a/output/pdf_financials_xlsx/GSS.xlsx
+++ b/output/pdf_financials_xlsx/GSS.xlsx
@@ -6054,7 +6054,7 @@
         <v>1.33411</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>1.421931</v>
+        <v>1.542002</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>1.544555</v>
@@ -6440,7 +6440,7 @@
         <v>-0.280609</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>0.045098</v>
+        <v>-0.045098</v>
       </c>
       <c r="L99" s="3" t="n">
         <v>-0.292453</v>
@@ -7553,7 +7553,7 @@
         <v>0</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>0.1785</v>
       </c>
       <c r="O118" s="3" t="n">
         <v>0</v>
@@ -15233,7 +15233,11 @@
           <t>Warrant reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -22774,7 +22778,7 @@
         <v>-0.280609</v>
       </c>
       <c r="N144" s="5" t="n">
-        <v>0.045098</v>
+        <v>-0.045098</v>
       </c>
       <c r="O144" s="5" t="n">
         <v>-0.292453</v>
@@ -23923,7 +23927,11 @@
           <t>Shares issued for exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -25442,7 +25450,11 @@
           <t>Shares issued for exploration and evaluation expenditures (Note 7(vii))</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GSS.xlsx
+++ b/output/pdf_financials_xlsx/GSS.xlsx
@@ -1108,7 +1108,7 @@
         <v>0</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.041668</v>
       </c>
       <c r="R12" s="1" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>-1.186047</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.643635</v>
+        <v>0.601967</v>
       </c>
       <c r="R27" s="1" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>-1.186047</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.643635</v>
+        <v>0.601967</v>
       </c>
       <c r="R29" s="1" t="inlineStr">
         <is>
@@ -2542,31 +2542,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.140692</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.496639</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.412548</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.379865</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.4957</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.194711</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.550791</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.243338</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.228798</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.494321</v>
@@ -2658,31 +2658,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>1.326653</v>
+        <v>1.467345</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.020004</v>
+        <v>0.516643</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.027408</v>
+        <v>0.439956</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.020004</v>
+        <v>1.399869</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.020004</v>
+        <v>0.5157040000000001</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.020004</v>
+        <v>0.214715</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.020029</v>
+        <v>0.57082</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.020029</v>
+        <v>0.263367</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.020229</v>
+        <v>0.249027</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0.523695</v>
@@ -3354,31 +3354,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.15288</v>
+        <v>0.012188</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.529404</v>
+        <v>0.032765</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.430782</v>
+        <v>0.018234</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.603194</v>
+        <v>0.223329</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.4957</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.300711</v>
+        <v>0.106</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.632076</v>
+        <v>0.081285</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.320943</v>
+        <v>0.07760499999999999</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.351915</v>
+        <v>0.123117</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -11350,7 +11350,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -15748,7 +15748,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -18651,7 +18651,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
@@ -34955,7 +34955,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
